--- a/AiKen_KEP_KEI.xlsx
+++ b/AiKen_KEP_KEI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nan\Documents\GitHub\code_aiken\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1820FFC-0734-4BF5-811F-AF36741AC1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1685AC28-3508-47AF-9730-B3B932014A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="144">
   <si>
     <t>领域</t>
   </si>
@@ -117,7 +117,7 @@
     <t>（产品规划，研发实现）</t>
   </si>
   <si>
-    <t>（S:业界最优；A: 我司最优；B: 我司中端设备应满足的标准）</t>
+    <t>S: Flashback One35 v2实测（待测）；A: AiKen目标（不劣于S，待定）；B: AiKen底线（科学分析值）</t>
   </si>
   <si>
     <t>拍摄体验</t>
@@ -149,16 +149,16 @@
     <t>过片计数+屏幕刷新</t>
   </si>
   <si>
-    <t>1.5s</t>
-  </si>
-  <si>
-    <t>2s</t>
+    <t>待测</t>
+  </si>
+  <si>
+    <t>待定</t>
   </si>
   <si>
     <t>3s</t>
   </si>
   <si>
-    <t>机械结构决定下限</t>
+    <t>机械过片+屏幕刷新，&gt;3s破坏快速抓拍感</t>
   </si>
   <si>
     <t>快门响应：按下快门到拍摄完成（剩余张数-1）</t>
@@ -172,16 +172,10 @@
     <t>快门事件+计数变更</t>
   </si>
   <si>
-    <t>100ms</t>
-  </si>
-  <si>
-    <t>150ms</t>
-  </si>
-  <si>
     <t>300ms</t>
   </si>
   <si>
-    <t>电子快门响应</t>
+    <t>Nielsen阈值：&gt;300ms用户怀疑按钮未响应</t>
   </si>
   <si>
     <t>连续拍摄周期：拍摄一张后过片再拍摄一张的完整周期</t>
@@ -195,13 +189,10 @@
     <t>过片+拍摄事件链</t>
   </si>
   <si>
-    <t>4s</t>
-  </si>
-  <si>
     <t>5s</t>
   </si>
   <si>
-    <t>含机械过片时间</t>
+    <t>含过片+拍摄，5s为连拍耐心极限</t>
   </si>
   <si>
     <t>冲扫模式</t>
@@ -224,7 +215,7 @@
     <t>10s</t>
   </si>
   <si>
-    <t>含蓝牙传输+风格化处理</t>
+    <t>Nielsen 10s阈值，"即时"模式底线</t>
   </si>
   <si>
     <t>经典冲扫</t>
@@ -241,16 +232,10 @@
     <t>冲扫完成通知</t>
   </si>
   <si>
-    <t>3h</t>
-  </si>
-  <si>
-    <t>12h</t>
-  </si>
-  <si>
     <t>24h</t>
   </si>
   <si>
-    <t>3~24小时随机取值</t>
+    <t>产品定义3-24h随机上限</t>
   </si>
   <si>
     <t>传输体验</t>
@@ -273,7 +258,7 @@
     <t>取出命令+设备状态变更</t>
   </si>
   <si>
-    <t>1s</t>
+    <t>BLE命令往返+状态切换，&gt;3s用户以为未开始</t>
   </si>
   <si>
     <t>单张照片传输耗时：传输一张照片的平均耗时</t>
@@ -287,13 +272,10 @@
     <t>单张传输起止事件</t>
   </si>
   <si>
-    <t>0.8s</t>
-  </si>
-  <si>
-    <t>1.2s</t>
-  </si>
-  <si>
-    <t>含裁切+JPEG压缩</t>
+    <t>2s</t>
+  </si>
+  <si>
+    <t>BLE吞吐100-200KB/s，JPEG 200-500KB，底线2s/张</t>
   </si>
   <si>
     <t>36张全量传输耗时：全部照片传输完成，计数器重置为36</t>
@@ -307,13 +289,10 @@
     <t>全量传输起止事件</t>
   </si>
   <si>
-    <t>30s</t>
-  </si>
-  <si>
-    <t>40s</t>
-  </si>
-  <si>
     <t>60s</t>
+  </si>
+  <si>
+    <t>60s耐心极限，屏幕无进度条无法显示进度</t>
   </si>
   <si>
     <t>打印机传输</t>
@@ -333,6 +312,9 @@
     <t>印放键事件+设备状态变更</t>
   </si>
   <si>
+    <t>同传输启动</t>
+  </si>
+  <si>
     <t>打印传输耗时：照片传输到打印机开始打印</t>
   </si>
   <si>
@@ -347,6 +329,9 @@
     <t>8s</t>
   </si>
   <si>
+    <t>单张传输+打印机握手，&gt;8s用户认为失败</t>
+  </si>
+  <si>
     <t>连接体验</t>
   </si>
   <si>
@@ -367,6 +352,9 @@
     <t>配对起止事件</t>
   </si>
   <si>
+    <t>BLE配对典型2-5s，10s为放弃阈值</t>
+  </si>
+  <si>
     <t>打印机配对</t>
   </si>
   <si>
@@ -378,6 +366,9 @@
 结束时间：设备指示灯蓝色常亮</t>
   </si>
   <si>
+    <t>同手机配对</t>
+  </si>
+  <si>
     <t>蓝牙重连</t>
   </si>
   <si>
@@ -395,6 +386,9 @@
     <t>重连起止事件</t>
   </si>
   <si>
+    <t>重连比首次快，&gt;5s用户会手动操作</t>
+  </si>
+  <si>
     <t>交互反馈体验</t>
   </si>
   <si>
@@ -415,7 +409,10 @@
     <t>印放键事件+状态反馈</t>
   </si>
   <si>
-    <t>200ms</t>
+    <t>按钮反馈300ms阈值</t>
+  </si>
+  <si>
+    <t>未连接打印机打印反馈：按下印放键到nP提示出现</t>
   </si>
   <si>
     <t>前置条件：设备未与打印机连接，有照片
@@ -423,6 +420,9 @@
 结束时间：屏幕nP闪烁+橙色指示灯闪烁</t>
   </si>
   <si>
+    <t>同上</t>
+  </si>
+  <si>
     <t>充电反馈</t>
   </si>
   <si>
@@ -437,6 +437,9 @@
     <t>电源接入事件+充电状态</t>
   </si>
   <si>
+    <t>USB-C协商+状态切换，&gt;3s用户检查充电器</t>
+  </si>
+  <si>
     <t>开关机</t>
   </si>
   <si>
@@ -454,7 +457,7 @@
     <t>开机事件+屏幕显示</t>
   </si>
   <si>
-    <t>含系统初始化时间</t>
+    <t>系统初始化，&gt;3s用户怀疑故障</t>
   </si>
   <si>
     <t>风格化体验</t>
@@ -477,6 +480,9 @@
     <t>风格切换命令+设备确认</t>
   </si>
   <si>
+    <t>BLE命令+设备确认，&gt;3s用户不确定</t>
+  </si>
+  <si>
     <t>风格解锁</t>
   </si>
   <si>
@@ -489,42 +495,13 @@
   </si>
   <si>
     <t>拍摄完成事件+解锁通知</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>未连接打印机打印反馈：按下印放键到</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>nP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提示出现</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -561,20 +538,14 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="微软雅黑"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -600,7 +571,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -678,12 +649,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -708,10 +694,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -722,18 +717,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1056,60 +1046,60 @@
     <col min="20" max="20" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
       <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="11" t="s">
+      <c r="Q1" s="19"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="T1" s="14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+    <row r="2" spans="1:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
       <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1124,8 +1114,8 @@
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
       <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
@@ -1135,10 +1125,10 @@
       <c r="R2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="13"/>
-      <c r="T2" s="12"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="15"/>
     </row>
-    <row r="3" spans="1:20" ht="45.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
@@ -1180,24 +1170,24 @@
       <c r="O3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="17"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="20"/>
       <c r="S3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T3" s="13"/>
+      <c r="T3" s="16"/>
     </row>
     <row r="4" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="17" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -1224,26 +1214,26 @@
       <c r="O4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="12" t="s">
         <v>42</v>
       </c>
       <c r="S4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="T4" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
       <c r="D5" s="5" t="s">
         <v>44</v>
       </c>
@@ -1268,28 +1258,28 @@
       <c r="O5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q5" s="6" t="s">
+      <c r="P5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1298,7 +1288,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -1310,34 +1300,34 @@
         <v>38</v>
       </c>
       <c r="O6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="14" t="s">
-        <v>57</v>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17" t="s">
+        <v>54</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>35</v>
@@ -1346,7 +1336,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
@@ -1358,32 +1348,32 @@
         <v>38</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T7" s="5" t="s">
-        <v>63</v>
+      <c r="T7" s="13" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>35</v>
@@ -1392,7 +1382,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -1404,36 +1394,36 @@
         <v>38</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R8" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="S8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T8" s="5" t="s">
-        <v>71</v>
+      <c r="T8" s="13" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>74</v>
+      <c r="A9" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>69</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>35</v>
@@ -1441,8 +1431,8 @@
       <c r="F9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="19" t="s">
-        <v>76</v>
+      <c r="G9" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -1454,28 +1444,30 @@
         <v>38</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="R9" s="6" t="s">
+      <c r="R9" s="12" t="s">
         <v>42</v>
       </c>
       <c r="S9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T9" s="5"/>
+      <c r="T9" s="13" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="10" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
       <c r="D10" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>35</v>
@@ -1483,8 +1475,8 @@
       <c r="F10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="19" t="s">
-        <v>80</v>
+      <c r="G10" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -1496,30 +1488,30 @@
         <v>38</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="R10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="12" t="s">
         <v>41</v>
       </c>
+      <c r="R10" s="12" t="s">
+        <v>77</v>
+      </c>
       <c r="S10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T10" s="5" t="s">
-        <v>84</v>
+      <c r="T10" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>35</v>
@@ -1527,8 +1519,8 @@
       <c r="F11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="19" t="s">
-        <v>86</v>
+      <c r="G11" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -1540,32 +1532,34 @@
         <v>38</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R11" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="S11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T11" s="5"/>
+      <c r="T11" s="13" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="12" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>92</v>
+      <c r="A12" s="15"/>
+      <c r="B12" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>35</v>
@@ -1573,8 +1567,8 @@
       <c r="F12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="19" t="s">
-        <v>94</v>
+      <c r="G12" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -1586,28 +1580,30 @@
         <v>38</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="R12" s="6" t="s">
+      <c r="R12" s="12" t="s">
         <v>42</v>
       </c>
       <c r="S12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T12" s="5"/>
+      <c r="T12" s="13" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="13" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
       <c r="D13" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>35</v>
@@ -1615,8 +1611,8 @@
       <c r="F13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="19" t="s">
-        <v>97</v>
+      <c r="G13" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -1628,34 +1624,36 @@
         <v>38</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q13" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>93</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T13" s="5"/>
+      <c r="T13" s="13" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="14" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>101</v>
+      <c r="A14" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>35</v>
@@ -1664,7 +1662,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -1676,30 +1674,32 @@
         <v>38</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>62</v>
+        <v>100</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R14" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T14" s="5"/>
+      <c r="T14" s="13" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="15" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>35</v>
@@ -1708,7 +1708,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -1720,32 +1720,34 @@
         <v>38</v>
       </c>
       <c r="O15" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="P15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="S15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="T15" s="5"/>
     </row>
     <row r="16" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="16"/>
       <c r="B16" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>35</v>
@@ -1754,7 +1756,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -1766,34 +1768,36 @@
         <v>38</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="P16" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q16" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="Q16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="R16" s="6" t="s">
-        <v>55</v>
+      <c r="R16" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="S16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T16" s="5"/>
+      <c r="T16" s="13" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="17" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="D17" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>35</v>
@@ -1802,7 +1806,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -1814,28 +1818,30 @@
         <v>38</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="P17" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q17" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R17" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="Q17" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="S17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T17" s="5"/>
+      <c r="T17" s="13" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="18" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="20" t="s">
-        <v>142</v>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>35</v>
@@ -1844,7 +1850,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -1856,25 +1862,27 @@
         <v>38</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="P18" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q18" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="Q18" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="R18" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="S18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T18" s="5"/>
+      <c r="T18" s="13" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="19" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="8" t="s">
         <v>122</v>
       </c>
@@ -1902,30 +1910,32 @@
       <c r="O19" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="P19" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q19" s="6" t="s">
+      <c r="P19" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q19" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="R19" s="6" t="s">
+      <c r="R19" s="12" t="s">
         <v>42</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T19" s="5"/>
+      <c r="T19" s="13" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="20" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>35</v>
@@ -1934,7 +1944,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -1946,36 +1956,36 @@
         <v>38</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="P20" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="Q20" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q20" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="R20" s="6" t="s">
-        <v>42</v>
+      <c r="R20" s="12">
+        <v>1</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T20" s="5" t="s">
-        <v>131</v>
+      <c r="T20" s="13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="17" t="s">
         <v>133</v>
       </c>
+      <c r="B21" s="17" t="s">
+        <v>134</v>
+      </c>
       <c r="C21" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>35</v>
@@ -1984,7 +1994,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -1996,30 +2006,32 @@
         <v>38</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="P21" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q21" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q21" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="R21" s="6" t="s">
+      <c r="R21" s="12" t="s">
         <v>42</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T21" s="5"/>
+      <c r="T21" s="13" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="22" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>35</v>
@@ -2028,7 +2040,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -2040,21 +2052,23 @@
         <v>38</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q22" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="P22" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q22" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="R22" s="6" t="s">
+      <c r="R22" s="12" t="s">
         <v>42</v>
       </c>
       <c r="S22" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T22" s="5"/>
+      <c r="T22" s="13" t="s">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -2062,7 +2076,6 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="A17:A20"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B7:B8"/>
@@ -2071,6 +2084,7 @@
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="B14:B15"/>
